--- a/题库/PY程序设计模拟题3.xlsx
+++ b/题库/PY程序设计模拟题3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="130">
   <si>
     <t>题号</t>
   </si>
@@ -204,6 +204,9 @@
     </r>
   </si>
   <si>
+    <t>5.5e3</t>
+  </si>
+  <si>
     <t>以下选项中，输出结果为False的是（）。</t>
   </si>
   <si>
@@ -213,7 +216,7 @@
     <t>'ABCD' == 'abcd'.upper()</t>
   </si>
   <si>
-    <t>"c" &lt; "a"</t>
+    <t>'&lt;'a'</t>
   </si>
   <si>
     <t>'python' &lt; 'pypi'</t>
@@ -427,7 +430,10 @@
     <t>dict={4:6}</t>
   </si>
   <si>
-    <t>dict={{4,5,6}: 'dictionary'}</t>
+    <t>dict={(4,5,6): 'dictionary'}</t>
+  </si>
+  <si>
+    <t>dict={[4,5,6]: 'dictionary'}</t>
   </si>
   <si>
     <t>填空</t>
@@ -1297,7 +1303,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1331,6 +1337,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="11" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1350,6 +1359,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1697,7 +1709,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1713,7 +1725,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="12"/>
+      <c r="J2" s="13"/>
     </row>
     <row r="3" ht="58" customHeight="1" spans="1:10">
       <c r="A3" s="2">
@@ -1743,7 +1755,7 @@
       <c r="I3" s="2">
         <v>2</v>
       </c>
-      <c r="J3" s="13"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2"/>
@@ -1755,7 +1767,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="14"/>
+      <c r="J4" s="15"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2"/>
@@ -1767,7 +1779,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="14"/>
+      <c r="J5" s="15"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2"/>
@@ -1779,7 +1791,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="14"/>
+      <c r="J6" s="15"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2"/>
@@ -1791,7 +1803,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="14"/>
+      <c r="J7" s="15"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2"/>
@@ -1803,7 +1815,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="14"/>
+      <c r="J8" s="15"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2"/>
@@ -1815,7 +1827,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="14"/>
+      <c r="J9" s="15"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2"/>
@@ -1827,7 +1839,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="14"/>
+      <c r="J10" s="15"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2"/>
@@ -1839,7 +1851,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="15"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" ht="43.5" customHeight="1" spans="1:10">
       <c r="A12" s="2">
@@ -1869,7 +1881,7 @@
       <c r="I12" s="2">
         <v>2</v>
       </c>
-      <c r="J12" s="13"/>
+      <c r="J12" s="14"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2"/>
@@ -1881,7 +1893,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="14"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2"/>
@@ -1893,7 +1905,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="15"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" ht="17" spans="1:10">
       <c r="A15" s="2">
@@ -1923,7 +1935,7 @@
       <c r="I15" s="2">
         <v>2</v>
       </c>
-      <c r="J15" s="12"/>
+      <c r="J15" s="13"/>
     </row>
     <row r="16" ht="58" customHeight="1" spans="1:10">
       <c r="A16" s="2">
@@ -1953,7 +1965,7 @@
       <c r="I16" s="2">
         <v>2</v>
       </c>
-      <c r="J16" s="13"/>
+      <c r="J16" s="14"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2"/>
@@ -1965,7 +1977,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="14"/>
+      <c r="J17" s="15"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2"/>
@@ -1977,7 +1989,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="14"/>
+      <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2"/>
@@ -1989,7 +2001,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="14"/>
+      <c r="J19" s="15"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2"/>
@@ -2001,7 +2013,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="14"/>
+      <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2"/>
@@ -2013,7 +2025,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="14"/>
+      <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2"/>
@@ -2025,7 +2037,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="14"/>
+      <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2"/>
@@ -2037,7 +2049,7 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="15"/>
+      <c r="J23" s="16"/>
     </row>
     <row r="24" ht="43.5" customHeight="1" spans="1:10">
       <c r="A24" s="2">
@@ -2049,13 +2061,13 @@
       <c r="C24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="11">
-        <v>5500</v>
+      <c r="D24" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="E24" s="2">
         <v>130.042</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="12">
         <v>5.5e+31</v>
       </c>
       <c r="G24" s="2">
@@ -2067,7 +2079,7 @@
       <c r="I24" s="2">
         <v>2</v>
       </c>
-      <c r="J24" s="13"/>
+      <c r="J24" s="14"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2"/>
@@ -2075,11 +2087,11 @@
       <c r="C25" s="9"/>
       <c r="D25" s="11"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="11"/>
+      <c r="F25" s="12"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="14"/>
+      <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2"/>
@@ -2087,11 +2099,11 @@
       <c r="C26" s="9"/>
       <c r="D26" s="11"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="11"/>
+      <c r="F26" s="12"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="14"/>
+      <c r="J26" s="15"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2"/>
@@ -2099,11 +2111,11 @@
       <c r="C27" s="10"/>
       <c r="D27" s="11"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="11"/>
+      <c r="F27" s="12"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="15"/>
+      <c r="J27" s="16"/>
     </row>
     <row r="28" ht="17" spans="1:10">
       <c r="A28" s="2">
@@ -2113,19 +2125,19 @@
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="F28" s="19" t="s">
+        <v>38</v>
+      </c>
       <c r="G28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>16</v>
@@ -2133,7 +2145,7 @@
       <c r="I28" s="2">
         <v>2</v>
       </c>
-      <c r="J28" s="12"/>
+      <c r="J28" s="13"/>
     </row>
     <row r="29" ht="17" spans="1:10">
       <c r="A29" s="2">
@@ -2143,13 +2155,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F29" s="2" t="b">
         <v>1</v>
@@ -2163,7 +2175,7 @@
       <c r="I29" s="2">
         <v>2</v>
       </c>
-      <c r="J29" s="12"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" ht="17" spans="1:10">
       <c r="A30" s="2">
@@ -2173,19 +2185,19 @@
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>22</v>
@@ -2193,7 +2205,7 @@
       <c r="I30" s="2">
         <v>2</v>
       </c>
-      <c r="J30" s="12"/>
+      <c r="J30" s="13"/>
     </row>
     <row r="31" ht="29" customHeight="1" spans="1:10">
       <c r="A31" s="2">
@@ -2203,19 +2215,19 @@
         <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>22</v>
@@ -2223,7 +2235,7 @@
       <c r="I31" s="2">
         <v>2</v>
       </c>
-      <c r="J31" s="13"/>
+      <c r="J31" s="14"/>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2"/>
@@ -2235,7 +2247,7 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="14"/>
+      <c r="J32" s="15"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2"/>
@@ -2247,7 +2259,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="14"/>
+      <c r="J33" s="15"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2"/>
@@ -2259,7 +2271,7 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="14"/>
+      <c r="J34" s="15"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2"/>
@@ -2271,7 +2283,7 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="14"/>
+      <c r="J35" s="15"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2"/>
@@ -2283,7 +2295,7 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="J36" s="14"/>
+      <c r="J36" s="15"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2"/>
@@ -2295,7 +2307,7 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="14"/>
+      <c r="J37" s="15"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="2"/>
@@ -2307,7 +2319,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="14"/>
+      <c r="J38" s="15"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="2"/>
@@ -2319,7 +2331,7 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="15"/>
+      <c r="J39" s="16"/>
     </row>
     <row r="40" ht="17" spans="1:10">
       <c r="A40" s="2">
@@ -2329,27 +2341,27 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I40" s="2">
         <v>2</v>
       </c>
-      <c r="J40" s="12"/>
+      <c r="J40" s="13"/>
     </row>
     <row r="41" ht="75" customHeight="1" spans="1:10">
       <c r="A41" s="2">
@@ -2359,7 +2371,7 @@
         <v>10</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2">
         <v>9</v>
@@ -2374,12 +2386,12 @@
         <v>1000</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I41" s="2">
         <v>2</v>
       </c>
-      <c r="J41" s="13"/>
+      <c r="J41" s="14"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="2"/>
@@ -2391,7 +2403,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="14"/>
+      <c r="J42" s="15"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2"/>
@@ -2403,7 +2415,7 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="14"/>
+      <c r="J43" s="15"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="2"/>
@@ -2415,7 +2427,7 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="14"/>
+      <c r="J44" s="15"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="2"/>
@@ -2427,7 +2439,7 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="15"/>
+      <c r="J45" s="16"/>
     </row>
     <row r="46" ht="17" spans="1:10">
       <c r="A46" s="2">
@@ -2437,27 +2449,27 @@
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I46" s="2">
         <v>2</v>
       </c>
-      <c r="J46" s="12"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" ht="43.5" customHeight="1" spans="1:10">
       <c r="A47" s="2">
@@ -2467,19 +2479,19 @@
         <v>10</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>22</v>
@@ -2487,7 +2499,7 @@
       <c r="I47" s="2">
         <v>2</v>
       </c>
-      <c r="J47" s="13"/>
+      <c r="J47" s="14"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2"/>
@@ -2499,7 +2511,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="14"/>
+      <c r="J48" s="15"/>
     </row>
     <row r="49" ht="17" spans="1:10">
       <c r="A49" s="2">
@@ -2509,27 +2521,27 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I49" s="2">
         <v>2</v>
       </c>
-      <c r="J49" s="16"/>
+      <c r="J49" s="17"/>
     </row>
     <row r="50" ht="17" spans="1:10">
       <c r="A50" s="2">
@@ -2539,19 +2551,19 @@
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>16</v>
@@ -2559,11 +2571,11 @@
       <c r="I50" s="2">
         <v>2</v>
       </c>
-      <c r="J50" s="12"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" ht="17" spans="1:10">
       <c r="A51" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2573,17 +2585,17 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="12"/>
+      <c r="J51" s="13"/>
     </row>
     <row r="52" ht="17" spans="1:10">
       <c r="A52" s="2">
         <v>16</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -2595,39 +2607,39 @@
       <c r="I52" s="2">
         <v>2</v>
       </c>
-      <c r="J52" s="12"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" ht="17" spans="1:10">
       <c r="A53" s="2">
         <v>17</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I53" s="2">
         <v>2</v>
       </c>
-      <c r="J53" s="12"/>
+      <c r="J53" s="13"/>
     </row>
     <row r="54" ht="17" spans="1:10">
       <c r="A54" s="2">
         <v>18</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -2639,61 +2651,61 @@
       <c r="I54" s="2">
         <v>2</v>
       </c>
-      <c r="J54" s="12"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" ht="17" spans="1:10">
       <c r="A55" s="2">
         <v>19</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I55" s="2">
         <v>2</v>
       </c>
-      <c r="J55" s="12"/>
+      <c r="J55" s="13"/>
     </row>
     <row r="56" ht="31.5" spans="1:10">
       <c r="A56" s="2">
         <v>20</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I56" s="2">
         <v>2</v>
       </c>
-      <c r="J56" s="12"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57" ht="17" spans="1:10">
       <c r="A57" s="2">
         <v>21</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -2705,61 +2717,61 @@
       <c r="I57" s="2">
         <v>2</v>
       </c>
-      <c r="J57" s="12"/>
+      <c r="J57" s="13"/>
     </row>
     <row r="58" ht="17" spans="1:10">
       <c r="A58" s="2">
         <v>22</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I58" s="2">
         <v>2</v>
       </c>
-      <c r="J58" s="12"/>
+      <c r="J58" s="13"/>
     </row>
     <row r="59" ht="34" spans="1:10">
       <c r="A59" s="2">
         <v>23</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I59" s="2">
         <v>2</v>
       </c>
-      <c r="J59" s="12"/>
+      <c r="J59" s="13"/>
     </row>
     <row r="60" ht="17" spans="1:10">
       <c r="A60" s="2">
         <v>24</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -2771,17 +2783,17 @@
       <c r="I60" s="2">
         <v>2</v>
       </c>
-      <c r="J60" s="12"/>
+      <c r="J60" s="13"/>
     </row>
     <row r="61" ht="17" spans="1:10">
       <c r="A61" s="2">
         <v>25</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
@@ -2793,17 +2805,17 @@
       <c r="I61" s="2">
         <v>2</v>
       </c>
-      <c r="J61" s="12"/>
+      <c r="J61" s="13"/>
     </row>
     <row r="62" ht="17" spans="1:10">
       <c r="A62" s="2">
         <v>26</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
@@ -2815,99 +2827,99 @@
       <c r="I62" s="2">
         <v>2</v>
       </c>
-      <c r="J62" s="12"/>
+      <c r="J62" s="13"/>
     </row>
     <row r="63" ht="17" spans="1:10">
       <c r="A63" s="2">
         <v>27</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I63" s="2">
         <v>2</v>
       </c>
-      <c r="J63" s="12"/>
+      <c r="J63" s="13"/>
     </row>
     <row r="64" ht="17" spans="1:10">
       <c r="A64" s="2">
         <v>28</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I64" s="2">
         <v>2</v>
       </c>
-      <c r="J64" s="12"/>
+      <c r="J64" s="13"/>
     </row>
     <row r="65" ht="17" spans="1:10">
       <c r="A65" s="2">
         <v>29</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I65" s="2">
         <v>2</v>
       </c>
-      <c r="J65" s="12"/>
+      <c r="J65" s="13"/>
     </row>
     <row r="66" ht="17" spans="1:10">
       <c r="A66" s="2">
         <v>30</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I66" s="2">
         <v>2</v>
       </c>
-      <c r="J66" s="12"/>
+      <c r="J66" s="13"/>
     </row>
     <row r="67" ht="17" spans="1:10">
       <c r="A67" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2917,271 +2929,271 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
-      <c r="J67" s="12"/>
+      <c r="J67" s="13"/>
     </row>
     <row r="68" ht="17" spans="1:10">
       <c r="A68" s="2">
         <v>31</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I68" s="2">
         <v>1</v>
       </c>
-      <c r="J68" s="12"/>
+      <c r="J68" s="13"/>
     </row>
     <row r="69" ht="17" spans="1:10">
       <c r="A69" s="2">
         <v>32</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="E69" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I69" s="2">
         <v>1</v>
       </c>
-      <c r="J69" s="12"/>
+      <c r="J69" s="13"/>
     </row>
     <row r="70" ht="17" spans="1:10">
       <c r="A70" s="2">
         <v>33</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I70" s="2">
         <v>1</v>
       </c>
-      <c r="J70" s="12"/>
+      <c r="J70" s="13"/>
     </row>
     <row r="71" ht="17" spans="1:10">
       <c r="A71" s="2">
         <v>34</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I71" s="2">
         <v>1</v>
       </c>
-      <c r="J71" s="12"/>
+      <c r="J71" s="13"/>
     </row>
     <row r="72" ht="17" spans="1:10">
       <c r="A72" s="2">
         <v>35</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I72" s="2">
         <v>1</v>
       </c>
-      <c r="J72" s="12"/>
+      <c r="J72" s="13"/>
     </row>
     <row r="73" ht="17" spans="1:10">
       <c r="A73" s="2">
         <v>36</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I73" s="2">
         <v>1</v>
       </c>
-      <c r="J73" s="12"/>
+      <c r="J73" s="13"/>
     </row>
     <row r="74" ht="17" spans="1:10">
       <c r="A74" s="2">
         <v>37</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I74" s="2">
         <v>1</v>
       </c>
-      <c r="J74" s="12"/>
+      <c r="J74" s="13"/>
     </row>
     <row r="75" ht="17" spans="1:10">
       <c r="A75" s="2">
         <v>38</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I75" s="2">
         <v>1</v>
       </c>
-      <c r="J75" s="12"/>
+      <c r="J75" s="13"/>
     </row>
     <row r="76" ht="17" spans="1:10">
       <c r="A76" s="2">
         <v>39</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I76" s="2">
         <v>1</v>
       </c>
-      <c r="J76" s="12"/>
+      <c r="J76" s="13"/>
     </row>
     <row r="77" ht="17" spans="1:10">
       <c r="A77" s="2">
         <v>40</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I77" s="2">
         <v>1</v>
       </c>
-      <c r="J77" s="12"/>
+      <c r="J77" s="13"/>
     </row>
     <row r="78" ht="17" spans="1:10">
       <c r="A78" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3191,30 +3203,30 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
-      <c r="J78" s="12"/>
+      <c r="J78" s="13"/>
     </row>
     <row r="79" ht="34" spans="1:10">
       <c r="A79" s="2">
         <v>41</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I79" s="2">
         <v>10</v>
       </c>
-      <c r="J79" s="12" t="s">
-        <v>120</v>
+      <c r="J79" s="13" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="80" ht="68" spans="1:10">
@@ -3222,28 +3234,28 @@
         <v>42</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="17" t="s">
-        <v>122</v>
+      <c r="H80" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="I80" s="2">
         <v>10</v>
       </c>
-      <c r="J80" s="12" t="s">
-        <v>123</v>
+      <c r="J80" s="13" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="81" ht="17" spans="1:10">
       <c r="A81" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3253,30 +3265,30 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
-      <c r="J81" s="12"/>
+      <c r="J81" s="13"/>
     </row>
     <row r="82" ht="51" spans="1:10">
       <c r="A82" s="2">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I82" s="2">
         <v>10</v>
       </c>
-      <c r="J82" s="12" t="s">
-        <v>127</v>
+      <c r="J82" s="13" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/题库/PY程序设计模拟题3.xlsx
+++ b/题库/PY程序设计模拟题3.xlsx
@@ -1303,15 +1303,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1322,14 +1322,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1338,13 +1335,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1355,14 +1352,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1675,45 +1669,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="8" width="68.8181818181818" customWidth="1"/>
+    <col min="1" max="10" width="10.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="17" spans="1:10">
+    <row r="2" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1725,9 +1719,9 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" ht="58" customHeight="1" spans="1:10">
+      <c r="J2" s="12"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1755,9 +1749,9 @@
       <c r="I3" s="2">
         <v>2</v>
       </c>
-      <c r="J3" s="14"/>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4"/>
@@ -1767,9 +1761,9 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="15"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="J4" s="14"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4"/>
@@ -1779,9 +1773,9 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="15"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="4"/>
@@ -1791,9 +1785,9 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="15"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="4"/>
@@ -1803,9 +1797,9 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="15"/>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="4"/>
@@ -1815,9 +1809,9 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="15"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="4"/>
@@ -1827,9 +1821,9 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="15"/>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="4"/>
@@ -1839,9 +1833,9 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="5"/>
@@ -1851,16 +1845,16 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" ht="43.5" customHeight="1" spans="1:10">
+      <c r="J11" s="15"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A12" s="2">
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -1881,33 +1875,33 @@
       <c r="I12" s="2">
         <v>2</v>
       </c>
-      <c r="J12" s="14"/>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="7"/>
+      <c r="C13" s="6"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="8"/>
+      <c r="C14" s="7"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="16"/>
-    </row>
-    <row r="15" ht="17" spans="1:10">
+      <c r="J14" s="15"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A15" s="2">
         <v>3</v>
       </c>
@@ -1935,9 +1929,9 @@
       <c r="I15" s="2">
         <v>2</v>
       </c>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16" ht="58" customHeight="1" spans="1:10">
+      <c r="J15" s="12"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A16" s="2">
         <v>4</v>
       </c>
@@ -1965,93 +1959,93 @@
       <c r="I16" s="2">
         <v>2</v>
       </c>
-      <c r="J16" s="14"/>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="9"/>
+      <c r="C17" s="8"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="15"/>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="9"/>
+      <c r="C18" s="8"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="9"/>
+      <c r="C19" s="8"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="15"/>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="9"/>
+      <c r="C20" s="8"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="9"/>
+      <c r="C21" s="8"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="9"/>
+      <c r="C22" s="8"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="15"/>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="16"/>
-    </row>
-    <row r="24" ht="43.5" customHeight="1" spans="1:10">
+      <c r="J23" s="15"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A24" s="2">
         <v>5</v>
       </c>
@@ -2061,13 +2055,13 @@
       <c r="C24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="10" t="s">
         <v>34</v>
       </c>
       <c r="E24" s="2">
         <v>130.042</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="11">
         <v>5.5e+31</v>
       </c>
       <c r="G24" s="2">
@@ -2079,45 +2073,45 @@
       <c r="I24" s="2">
         <v>2</v>
       </c>
-      <c r="J24" s="14"/>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="11"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="10"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="15"/>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="11"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="10"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="15"/>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="11"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="16"/>
-    </row>
-    <row r="28" ht="17" spans="1:10">
+      <c r="J27" s="15"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A28" s="2">
         <v>6</v>
       </c>
@@ -2133,7 +2127,7 @@
       <c r="E28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="17" t="s">
         <v>38</v>
       </c>
       <c r="G28" s="2" t="s">
@@ -2145,9 +2139,9 @@
       <c r="I28" s="2">
         <v>2</v>
       </c>
-      <c r="J28" s="13"/>
-    </row>
-    <row r="29" ht="17" spans="1:10">
+      <c r="J28" s="12"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A29" s="2">
         <v>7</v>
       </c>
@@ -2175,9 +2169,9 @@
       <c r="I29" s="2">
         <v>2</v>
       </c>
-      <c r="J29" s="13"/>
-    </row>
-    <row r="30" ht="17" spans="1:10">
+      <c r="J29" s="12"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A30" s="2">
         <v>8</v>
       </c>
@@ -2205,9 +2199,9 @@
       <c r="I30" s="2">
         <v>2</v>
       </c>
-      <c r="J30" s="13"/>
-    </row>
-    <row r="31" ht="29" customHeight="1" spans="1:10">
+      <c r="J30" s="12"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A31" s="2">
         <v>9</v>
       </c>
@@ -2235,105 +2229,105 @@
       <c r="I31" s="2">
         <v>2</v>
       </c>
-      <c r="J31" s="14"/>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="J31" s="13"/>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="9"/>
+      <c r="C32" s="8"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="9"/>
+      <c r="C33" s="8"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="9"/>
+      <c r="C34" s="8"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="9"/>
+      <c r="C35" s="8"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="15"/>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="9"/>
+      <c r="C36" s="8"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="J36" s="15"/>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="9"/>
+      <c r="C37" s="8"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="15"/>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="9"/>
+      <c r="C38" s="8"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="15"/>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="16"/>
-    </row>
-    <row r="40" ht="17" spans="1:10">
+      <c r="J39" s="15"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A40" s="2">
         <v>10</v>
       </c>
@@ -2361,9 +2355,9 @@
       <c r="I40" s="2">
         <v>2</v>
       </c>
-      <c r="J40" s="13"/>
-    </row>
-    <row r="41" ht="75" customHeight="1" spans="1:10">
+      <c r="J40" s="12"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A41" s="2">
         <v>11</v>
       </c>
@@ -2391,57 +2385,57 @@
       <c r="I41" s="2">
         <v>2</v>
       </c>
-      <c r="J41" s="14"/>
-    </row>
-    <row r="42" spans="1:10">
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="9"/>
+      <c r="C42" s="8"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:10">
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
-      <c r="C43" s="9"/>
+      <c r="C43" s="8"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="15"/>
-    </row>
-    <row r="44" spans="1:10">
+      <c r="J43" s="14"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
-      <c r="C44" s="9"/>
+      <c r="C44" s="8"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="45" spans="1:10">
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="16"/>
-    </row>
-    <row r="46" ht="17" spans="1:10">
+      <c r="J45" s="15"/>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A46" s="2">
         <v>12</v>
       </c>
@@ -2469,9 +2463,9 @@
       <c r="I46" s="2">
         <v>2</v>
       </c>
-      <c r="J46" s="13"/>
-    </row>
-    <row r="47" ht="43.5" customHeight="1" spans="1:10">
+      <c r="J46" s="12"/>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A47" s="2">
         <v>13</v>
       </c>
@@ -2499,21 +2493,21 @@
       <c r="I47" s="2">
         <v>2</v>
       </c>
-      <c r="J47" s="14"/>
-    </row>
-    <row r="48" spans="1:10">
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-      <c r="C48" s="10"/>
+      <c r="C48" s="9"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="15"/>
-    </row>
-    <row r="49" ht="17" spans="1:10">
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A49" s="2">
         <v>14</v>
       </c>
@@ -2541,9 +2535,9 @@
       <c r="I49" s="2">
         <v>2</v>
       </c>
-      <c r="J49" s="17"/>
-    </row>
-    <row r="50" ht="17" spans="1:10">
+      <c r="J49" s="15"/>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A50" s="2">
         <v>15</v>
       </c>
@@ -2571,9 +2565,9 @@
       <c r="I50" s="2">
         <v>2</v>
       </c>
-      <c r="J50" s="13"/>
-    </row>
-    <row r="51" ht="17" spans="1:10">
+      <c r="J50" s="12"/>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A51" s="2" t="s">
         <v>81</v>
       </c>
@@ -2585,9 +2579,9 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="13"/>
-    </row>
-    <row r="52" ht="17" spans="1:10">
+      <c r="J51" s="12"/>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A52" s="2">
         <v>16</v>
       </c>
@@ -2607,9 +2601,9 @@
       <c r="I52" s="2">
         <v>2</v>
       </c>
-      <c r="J52" s="13"/>
-    </row>
-    <row r="53" ht="17" spans="1:10">
+      <c r="J52" s="12"/>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A53" s="2">
         <v>17</v>
       </c>
@@ -2629,9 +2623,9 @@
       <c r="I53" s="2">
         <v>2</v>
       </c>
-      <c r="J53" s="13"/>
-    </row>
-    <row r="54" ht="17" spans="1:10">
+      <c r="J53" s="12"/>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A54" s="2">
         <v>18</v>
       </c>
@@ -2651,9 +2645,9 @@
       <c r="I54" s="2">
         <v>2</v>
       </c>
-      <c r="J54" s="13"/>
-    </row>
-    <row r="55" ht="17" spans="1:10">
+      <c r="J54" s="12"/>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A55" s="2">
         <v>19</v>
       </c>
@@ -2673,9 +2667,9 @@
       <c r="I55" s="2">
         <v>2</v>
       </c>
-      <c r="J55" s="13"/>
-    </row>
-    <row r="56" ht="31.5" spans="1:10">
+      <c r="J55" s="12"/>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A56" s="2">
         <v>20</v>
       </c>
@@ -2695,9 +2689,9 @@
       <c r="I56" s="2">
         <v>2</v>
       </c>
-      <c r="J56" s="13"/>
-    </row>
-    <row r="57" ht="17" spans="1:10">
+      <c r="J56" s="12"/>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A57" s="2">
         <v>21</v>
       </c>
@@ -2717,9 +2711,9 @@
       <c r="I57" s="2">
         <v>2</v>
       </c>
-      <c r="J57" s="13"/>
-    </row>
-    <row r="58" ht="17" spans="1:10">
+      <c r="J57" s="12"/>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A58" s="2">
         <v>22</v>
       </c>
@@ -2739,9 +2733,9 @@
       <c r="I58" s="2">
         <v>2</v>
       </c>
-      <c r="J58" s="13"/>
-    </row>
-    <row r="59" ht="34" spans="1:10">
+      <c r="J58" s="12"/>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A59" s="2">
         <v>23</v>
       </c>
@@ -2761,9 +2755,9 @@
       <c r="I59" s="2">
         <v>2</v>
       </c>
-      <c r="J59" s="13"/>
-    </row>
-    <row r="60" ht="17" spans="1:10">
+      <c r="J59" s="12"/>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A60" s="2">
         <v>24</v>
       </c>
@@ -2783,9 +2777,9 @@
       <c r="I60" s="2">
         <v>2</v>
       </c>
-      <c r="J60" s="13"/>
-    </row>
-    <row r="61" ht="17" spans="1:10">
+      <c r="J60" s="12"/>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A61" s="2">
         <v>25</v>
       </c>
@@ -2805,9 +2799,9 @@
       <c r="I61" s="2">
         <v>2</v>
       </c>
-      <c r="J61" s="13"/>
-    </row>
-    <row r="62" ht="17" spans="1:10">
+      <c r="J61" s="12"/>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A62" s="2">
         <v>26</v>
       </c>
@@ -2827,9 +2821,9 @@
       <c r="I62" s="2">
         <v>2</v>
       </c>
-      <c r="J62" s="13"/>
-    </row>
-    <row r="63" ht="17" spans="1:10">
+      <c r="J62" s="12"/>
+    </row>
+    <row r="63" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A63" s="2">
         <v>27</v>
       </c>
@@ -2849,9 +2843,9 @@
       <c r="I63" s="2">
         <v>2</v>
       </c>
-      <c r="J63" s="13"/>
-    </row>
-    <row r="64" ht="17" spans="1:10">
+      <c r="J63" s="12"/>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A64" s="2">
         <v>28</v>
       </c>
@@ -2871,9 +2865,9 @@
       <c r="I64" s="2">
         <v>2</v>
       </c>
-      <c r="J64" s="13"/>
-    </row>
-    <row r="65" ht="17" spans="1:10">
+      <c r="J64" s="12"/>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A65" s="2">
         <v>29</v>
       </c>
@@ -2893,9 +2887,9 @@
       <c r="I65" s="2">
         <v>2</v>
       </c>
-      <c r="J65" s="13"/>
-    </row>
-    <row r="66" ht="17" spans="1:10">
+      <c r="J65" s="12"/>
+    </row>
+    <row r="66" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A66" s="2">
         <v>30</v>
       </c>
@@ -2915,9 +2909,9 @@
       <c r="I66" s="2">
         <v>2</v>
       </c>
-      <c r="J66" s="13"/>
-    </row>
-    <row r="67" ht="17" spans="1:10">
+      <c r="J66" s="12"/>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A67" s="2" t="s">
         <v>106</v>
       </c>
@@ -2929,9 +2923,9 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
-      <c r="J67" s="13"/>
-    </row>
-    <row r="68" ht="17" spans="1:10">
+      <c r="J67" s="12"/>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A68" s="2">
         <v>31</v>
       </c>
@@ -2955,9 +2949,9 @@
       <c r="I68" s="2">
         <v>1</v>
       </c>
-      <c r="J68" s="13"/>
-    </row>
-    <row r="69" ht="17" spans="1:10">
+      <c r="J68" s="12"/>
+    </row>
+    <row r="69" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A69" s="2">
         <v>32</v>
       </c>
@@ -2981,9 +2975,9 @@
       <c r="I69" s="2">
         <v>1</v>
       </c>
-      <c r="J69" s="13"/>
-    </row>
-    <row r="70" ht="17" spans="1:10">
+      <c r="J69" s="12"/>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A70" s="2">
         <v>33</v>
       </c>
@@ -3007,9 +3001,9 @@
       <c r="I70" s="2">
         <v>1</v>
       </c>
-      <c r="J70" s="13"/>
-    </row>
-    <row r="71" ht="17" spans="1:10">
+      <c r="J70" s="12"/>
+    </row>
+    <row r="71" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A71" s="2">
         <v>34</v>
       </c>
@@ -3033,9 +3027,9 @@
       <c r="I71" s="2">
         <v>1</v>
       </c>
-      <c r="J71" s="13"/>
-    </row>
-    <row r="72" ht="17" spans="1:10">
+      <c r="J71" s="12"/>
+    </row>
+    <row r="72" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A72" s="2">
         <v>35</v>
       </c>
@@ -3059,9 +3053,9 @@
       <c r="I72" s="2">
         <v>1</v>
       </c>
-      <c r="J72" s="13"/>
-    </row>
-    <row r="73" ht="17" spans="1:10">
+      <c r="J72" s="12"/>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A73" s="2">
         <v>36</v>
       </c>
@@ -3085,9 +3079,9 @@
       <c r="I73" s="2">
         <v>1</v>
       </c>
-      <c r="J73" s="13"/>
-    </row>
-    <row r="74" ht="17" spans="1:10">
+      <c r="J73" s="12"/>
+    </row>
+    <row r="74" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A74" s="2">
         <v>37</v>
       </c>
@@ -3111,9 +3105,9 @@
       <c r="I74" s="2">
         <v>1</v>
       </c>
-      <c r="J74" s="13"/>
-    </row>
-    <row r="75" ht="17" spans="1:10">
+      <c r="J74" s="12"/>
+    </row>
+    <row r="75" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A75" s="2">
         <v>38</v>
       </c>
@@ -3137,9 +3131,9 @@
       <c r="I75" s="2">
         <v>1</v>
       </c>
-      <c r="J75" s="13"/>
-    </row>
-    <row r="76" ht="17" spans="1:10">
+      <c r="J75" s="12"/>
+    </row>
+    <row r="76" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A76" s="2">
         <v>39</v>
       </c>
@@ -3163,9 +3157,9 @@
       <c r="I76" s="2">
         <v>1</v>
       </c>
-      <c r="J76" s="13"/>
-    </row>
-    <row r="77" ht="17" spans="1:10">
+      <c r="J76" s="12"/>
+    </row>
+    <row r="77" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A77" s="2">
         <v>40</v>
       </c>
@@ -3189,9 +3183,9 @@
       <c r="I77" s="2">
         <v>1</v>
       </c>
-      <c r="J77" s="13"/>
-    </row>
-    <row r="78" ht="17" spans="1:10">
+      <c r="J77" s="12"/>
+    </row>
+    <row r="78" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A78" s="2" t="s">
         <v>119</v>
       </c>
@@ -3203,9 +3197,9 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
-      <c r="J78" s="13"/>
-    </row>
-    <row r="79" ht="34" spans="1:10">
+      <c r="J78" s="12"/>
+    </row>
+    <row r="79" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A79" s="2">
         <v>41</v>
       </c>
@@ -3225,11 +3219,11 @@
       <c r="I79" s="2">
         <v>10</v>
       </c>
-      <c r="J79" s="13" t="s">
+      <c r="J79" s="12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="80" ht="68" spans="1:10">
+    <row r="80" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A80" s="2">
         <v>42</v>
       </c>
@@ -3243,17 +3237,17 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="18" t="s">
+      <c r="H80" s="16" t="s">
         <v>124</v>
       </c>
       <c r="I80" s="2">
         <v>10</v>
       </c>
-      <c r="J80" s="13" t="s">
+      <c r="J80" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="81" ht="17" spans="1:10">
+    <row r="81" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A81" s="2" t="s">
         <v>126</v>
       </c>
@@ -3265,9 +3259,9 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
-      <c r="J81" s="13"/>
-    </row>
-    <row r="82" ht="51" spans="1:10">
+      <c r="J81" s="12"/>
+    </row>
+    <row r="82" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A82" s="2">
         <v>43</v>
       </c>
@@ -3287,10 +3281,12 @@
       <c r="I82" s="2">
         <v>10</v>
       </c>
-      <c r="J82" s="13" t="s">
+      <c r="J82" s="12" t="s">
         <v>129</v>
       </c>
     </row>
+    <row r="83" ht="44" customHeight="1"/>
+    <row r="84" ht="44" customHeight="1"/>
   </sheetData>
   <mergeCells count="70">
     <mergeCell ref="A3:A11"/>

--- a/题库/PY程序设计模拟题3.xlsx
+++ b/题库/PY程序设计模拟题3.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="131">
   <si>
     <t>题号</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>5.5e3</t>
+  </si>
+  <si>
+    <t>5.5e31</t>
   </si>
   <si>
     <t>以下选项中，输出结果为False的是（）。</t>
@@ -1303,7 +1306,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1335,9 +1338,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1703,7 +1703,7 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="12"/>
+      <c r="J2" s="11"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A3" s="2">
@@ -1749,7 +1749,7 @@
       <c r="I3" s="2">
         <v>2</v>
       </c>
-      <c r="J3" s="13"/>
+      <c r="J3" s="12"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
@@ -1761,7 +1761,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="14"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
@@ -1773,7 +1773,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="14"/>
+      <c r="J5" s="13"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A6" s="2"/>
@@ -1785,7 +1785,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="14"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A7" s="2"/>
@@ -1797,7 +1797,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="14"/>
+      <c r="J7" s="13"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A8" s="2"/>
@@ -1809,7 +1809,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="14"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A9" s="2"/>
@@ -1821,7 +1821,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="14"/>
+      <c r="J9" s="13"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A10" s="2"/>
@@ -1833,7 +1833,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="14"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A11" s="2"/>
@@ -1845,7 +1845,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="15"/>
+      <c r="J11" s="14"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A12" s="2">
@@ -1875,7 +1875,7 @@
       <c r="I12" s="2">
         <v>2</v>
       </c>
-      <c r="J12" s="13"/>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A13" s="2"/>
@@ -1887,7 +1887,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="14"/>
+      <c r="J13" s="13"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A14" s="2"/>
@@ -1899,7 +1899,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="15"/>
+      <c r="J14" s="14"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A15" s="2">
@@ -1929,7 +1929,7 @@
       <c r="I15" s="2">
         <v>2</v>
       </c>
-      <c r="J15" s="12"/>
+      <c r="J15" s="11"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A16" s="2">
@@ -1959,7 +1959,7 @@
       <c r="I16" s="2">
         <v>2</v>
       </c>
-      <c r="J16" s="13"/>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A17" s="2"/>
@@ -1971,7 +1971,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="14"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A18" s="2"/>
@@ -1983,7 +1983,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="14"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A19" s="2"/>
@@ -1995,7 +1995,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="14"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A20" s="2"/>
@@ -2007,7 +2007,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="14"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A21" s="2"/>
@@ -2019,7 +2019,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="14"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A22" s="2"/>
@@ -2031,7 +2031,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="14"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A23" s="2"/>
@@ -2043,7 +2043,7 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="15"/>
+      <c r="J23" s="14"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A24" s="2">
@@ -2061,8 +2061,8 @@
       <c r="E24" s="2">
         <v>130.042</v>
       </c>
-      <c r="F24" s="11">
-        <v>5.5e+31</v>
+      <c r="F24" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="G24" s="2">
         <v>130.42</v>
@@ -2073,7 +2073,7 @@
       <c r="I24" s="2">
         <v>2</v>
       </c>
-      <c r="J24" s="13"/>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A25" s="2"/>
@@ -2081,11 +2081,11 @@
       <c r="C25" s="8"/>
       <c r="D25" s="10"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="11"/>
+      <c r="F25" s="10"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="14"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A26" s="2"/>
@@ -2093,11 +2093,11 @@
       <c r="C26" s="8"/>
       <c r="D26" s="10"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="11"/>
+      <c r="F26" s="10"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="14"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A27" s="2"/>
@@ -2105,11 +2105,11 @@
       <c r="C27" s="9"/>
       <c r="D27" s="10"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="11"/>
+      <c r="F27" s="10"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="15"/>
+      <c r="J27" s="14"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A28" s="2">
@@ -2119,19 +2119,19 @@
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="F28" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="G28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>16</v>
@@ -2139,7 +2139,7 @@
       <c r="I28" s="2">
         <v>2</v>
       </c>
-      <c r="J28" s="12"/>
+      <c r="J28" s="11"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A29" s="2">
@@ -2149,13 +2149,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F29" s="2" t="b">
         <v>1</v>
@@ -2169,7 +2169,7 @@
       <c r="I29" s="2">
         <v>2</v>
       </c>
-      <c r="J29" s="12"/>
+      <c r="J29" s="11"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A30" s="2">
@@ -2179,19 +2179,19 @@
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>22</v>
@@ -2199,7 +2199,7 @@
       <c r="I30" s="2">
         <v>2</v>
       </c>
-      <c r="J30" s="12"/>
+      <c r="J30" s="11"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A31" s="2">
@@ -2209,19 +2209,19 @@
         <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>22</v>
@@ -2229,7 +2229,7 @@
       <c r="I31" s="2">
         <v>2</v>
       </c>
-      <c r="J31" s="13"/>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A32" s="2"/>
@@ -2241,7 +2241,7 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="14"/>
+      <c r="J32" s="13"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A33" s="2"/>
@@ -2253,7 +2253,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="14"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A34" s="2"/>
@@ -2265,7 +2265,7 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="14"/>
+      <c r="J34" s="13"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A35" s="2"/>
@@ -2277,7 +2277,7 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="14"/>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A36" s="2"/>
@@ -2289,7 +2289,7 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="J36" s="14"/>
+      <c r="J36" s="13"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A37" s="2"/>
@@ -2301,7 +2301,7 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="14"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A38" s="2"/>
@@ -2313,7 +2313,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="14"/>
+      <c r="J38" s="13"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A39" s="2"/>
@@ -2325,7 +2325,7 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="15"/>
+      <c r="J39" s="14"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A40" s="2">
@@ -2335,27 +2335,27 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I40" s="2">
         <v>2</v>
       </c>
-      <c r="J40" s="12"/>
+      <c r="J40" s="11"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A41" s="2">
@@ -2365,7 +2365,7 @@
         <v>10</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D41" s="2">
         <v>9</v>
@@ -2380,12 +2380,12 @@
         <v>1000</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I41" s="2">
         <v>2</v>
       </c>
-      <c r="J41" s="13"/>
+      <c r="J41" s="12"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A42" s="2"/>
@@ -2397,7 +2397,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="14"/>
+      <c r="J42" s="13"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A43" s="2"/>
@@ -2409,7 +2409,7 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="14"/>
+      <c r="J43" s="13"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A44" s="2"/>
@@ -2421,7 +2421,7 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="14"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A45" s="2"/>
@@ -2433,7 +2433,7 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="15"/>
+      <c r="J45" s="14"/>
     </row>
     <row r="46" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A46" s="2">
@@ -2443,27 +2443,27 @@
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I46" s="2">
         <v>2</v>
       </c>
-      <c r="J46" s="12"/>
+      <c r="J46" s="11"/>
     </row>
     <row r="47" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A47" s="2">
@@ -2473,19 +2473,19 @@
         <v>10</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>22</v>
@@ -2493,7 +2493,7 @@
       <c r="I47" s="2">
         <v>2</v>
       </c>
-      <c r="J47" s="13"/>
+      <c r="J47" s="12"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A48" s="2"/>
@@ -2505,7 +2505,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="14"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A49" s="2">
@@ -2515,27 +2515,27 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I49" s="2">
         <v>2</v>
       </c>
-      <c r="J49" s="15"/>
+      <c r="J49" s="14"/>
     </row>
     <row r="50" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A50" s="2">
@@ -2545,19 +2545,19 @@
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>16</v>
@@ -2565,11 +2565,11 @@
       <c r="I50" s="2">
         <v>2</v>
       </c>
-      <c r="J50" s="12"/>
+      <c r="J50" s="11"/>
     </row>
     <row r="51" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A51" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2579,17 +2579,17 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="12"/>
+      <c r="J51" s="11"/>
     </row>
     <row r="52" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A52" s="2">
         <v>16</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -2601,39 +2601,39 @@
       <c r="I52" s="2">
         <v>2</v>
       </c>
-      <c r="J52" s="12"/>
+      <c r="J52" s="11"/>
     </row>
     <row r="53" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A53" s="2">
         <v>17</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I53" s="2">
         <v>2</v>
       </c>
-      <c r="J53" s="12"/>
+      <c r="J53" s="11"/>
     </row>
     <row r="54" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A54" s="2">
         <v>18</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -2645,61 +2645,61 @@
       <c r="I54" s="2">
         <v>2</v>
       </c>
-      <c r="J54" s="12"/>
+      <c r="J54" s="11"/>
     </row>
     <row r="55" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A55" s="2">
         <v>19</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I55" s="2">
         <v>2</v>
       </c>
-      <c r="J55" s="12"/>
+      <c r="J55" s="11"/>
     </row>
     <row r="56" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A56" s="2">
         <v>20</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I56" s="2">
         <v>2</v>
       </c>
-      <c r="J56" s="12"/>
+      <c r="J56" s="11"/>
     </row>
     <row r="57" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A57" s="2">
         <v>21</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -2711,61 +2711,61 @@
       <c r="I57" s="2">
         <v>2</v>
       </c>
-      <c r="J57" s="12"/>
+      <c r="J57" s="11"/>
     </row>
     <row r="58" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A58" s="2">
         <v>22</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I58" s="2">
         <v>2</v>
       </c>
-      <c r="J58" s="12"/>
+      <c r="J58" s="11"/>
     </row>
     <row r="59" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A59" s="2">
         <v>23</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I59" s="2">
         <v>2</v>
       </c>
-      <c r="J59" s="12"/>
+      <c r="J59" s="11"/>
     </row>
     <row r="60" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A60" s="2">
         <v>24</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -2777,17 +2777,17 @@
       <c r="I60" s="2">
         <v>2</v>
       </c>
-      <c r="J60" s="12"/>
+      <c r="J60" s="11"/>
     </row>
     <row r="61" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A61" s="2">
         <v>25</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
@@ -2799,17 +2799,17 @@
       <c r="I61" s="2">
         <v>2</v>
       </c>
-      <c r="J61" s="12"/>
+      <c r="J61" s="11"/>
     </row>
     <row r="62" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A62" s="2">
         <v>26</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
@@ -2821,99 +2821,99 @@
       <c r="I62" s="2">
         <v>2</v>
       </c>
-      <c r="J62" s="12"/>
+      <c r="J62" s="11"/>
     </row>
     <row r="63" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A63" s="2">
         <v>27</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I63" s="2">
         <v>2</v>
       </c>
-      <c r="J63" s="12"/>
+      <c r="J63" s="11"/>
     </row>
     <row r="64" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A64" s="2">
         <v>28</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I64" s="2">
         <v>2</v>
       </c>
-      <c r="J64" s="12"/>
+      <c r="J64" s="11"/>
     </row>
     <row r="65" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A65" s="2">
         <v>29</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I65" s="2">
         <v>2</v>
       </c>
-      <c r="J65" s="12"/>
+      <c r="J65" s="11"/>
     </row>
     <row r="66" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A66" s="2">
         <v>30</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I66" s="2">
         <v>2</v>
       </c>
-      <c r="J66" s="12"/>
+      <c r="J66" s="11"/>
     </row>
     <row r="67" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A67" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2923,271 +2923,271 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
-      <c r="J67" s="12"/>
+      <c r="J67" s="11"/>
     </row>
     <row r="68" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A68" s="2">
         <v>31</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I68" s="2">
         <v>1</v>
       </c>
-      <c r="J68" s="12"/>
+      <c r="J68" s="11"/>
     </row>
     <row r="69" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A69" s="2">
         <v>32</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I69" s="2">
         <v>1</v>
       </c>
-      <c r="J69" s="12"/>
+      <c r="J69" s="11"/>
     </row>
     <row r="70" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A70" s="2">
         <v>33</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I70" s="2">
         <v>1</v>
       </c>
-      <c r="J70" s="12"/>
+      <c r="J70" s="11"/>
     </row>
     <row r="71" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A71" s="2">
         <v>34</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I71" s="2">
         <v>1</v>
       </c>
-      <c r="J71" s="12"/>
+      <c r="J71" s="11"/>
     </row>
     <row r="72" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A72" s="2">
         <v>35</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I72" s="2">
         <v>1</v>
       </c>
-      <c r="J72" s="12"/>
+      <c r="J72" s="11"/>
     </row>
     <row r="73" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A73" s="2">
         <v>36</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I73" s="2">
         <v>1</v>
       </c>
-      <c r="J73" s="12"/>
+      <c r="J73" s="11"/>
     </row>
     <row r="74" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A74" s="2">
         <v>37</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I74" s="2">
         <v>1</v>
       </c>
-      <c r="J74" s="12"/>
+      <c r="J74" s="11"/>
     </row>
     <row r="75" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A75" s="2">
         <v>38</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I75" s="2">
         <v>1</v>
       </c>
-      <c r="J75" s="12"/>
+      <c r="J75" s="11"/>
     </row>
     <row r="76" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A76" s="2">
         <v>39</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I76" s="2">
         <v>1</v>
       </c>
-      <c r="J76" s="12"/>
+      <c r="J76" s="11"/>
     </row>
     <row r="77" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A77" s="2">
         <v>40</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I77" s="2">
         <v>1</v>
       </c>
-      <c r="J77" s="12"/>
+      <c r="J77" s="11"/>
     </row>
     <row r="78" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A78" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3197,30 +3197,30 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
-      <c r="J78" s="12"/>
+      <c r="J78" s="11"/>
     </row>
     <row r="79" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A79" s="2">
         <v>41</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I79" s="2">
         <v>10</v>
       </c>
-      <c r="J79" s="12" t="s">
-        <v>122</v>
+      <c r="J79" s="11" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
@@ -3228,28 +3228,28 @@
         <v>42</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="16" t="s">
-        <v>124</v>
+      <c r="H80" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="I80" s="2">
         <v>10</v>
       </c>
-      <c r="J80" s="12" t="s">
-        <v>125</v>
+      <c r="J80" s="11" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A81" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3259,30 +3259,30 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
-      <c r="J81" s="12"/>
+      <c r="J81" s="11"/>
     </row>
     <row r="82" s="1" customFormat="1" ht="55" customHeight="1" spans="1:10">
       <c r="A82" s="2">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I82" s="2">
         <v>10</v>
       </c>
-      <c r="J82" s="12" t="s">
-        <v>129</v>
+      <c r="J82" s="11" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="83" ht="44" customHeight="1"/>
